--- a/data/trans_orig/P05A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>607944</t>
+          <t>609904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>639459</t>
+          <t>640434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>606621</t>
+          <t>606878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>637496</t>
+          <t>637109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1227842</t>
+          <t>1227841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1270555</t>
+          <t>1270806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46714</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76332</t>
+          <t>76484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63963</t>
+          <t>63350</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>90491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128644</t>
+          <t>129306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>28607</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>841621</t>
+          <t>838694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>879634</t>
+          <t>878075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>838171</t>
+          <t>839245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>879158</t>
+          <t>879859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1692268</t>
+          <t>1692589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1746967</t>
+          <t>1748027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60491</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96716</t>
+          <t>97171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59448</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95821</t>
+          <t>93710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>128263</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>180258</t>
+          <t>178820</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32032</t>
+          <t>32825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62044</t>
+          <t>61622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>568229</t>
+          <t>567184</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>604957</t>
+          <t>603599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>583111</t>
+          <t>584907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>616135</t>
+          <t>618664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1162423</t>
+          <t>1165418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1213689</t>
+          <t>1211969</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61266</t>
+          <t>61658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96568</t>
+          <t>96765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51032</t>
+          <t>50386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81773</t>
+          <t>81269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118446</t>
+          <t>120909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166830</t>
+          <t>165793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33385</t>
+          <t>34479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>803298</t>
+          <t>803087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>840075</t>
+          <t>839903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>877147</t>
+          <t>877890</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>918461</t>
+          <t>919329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1694388</t>
+          <t>1693975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1750847</t>
+          <t>1749025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59986</t>
+          <t>59112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91239</t>
+          <t>90286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79280</t>
+          <t>79178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117400</t>
+          <t>115691</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146729</t>
+          <t>146674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197217</t>
+          <t>196333</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>36762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>33170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59945</t>
+          <t>59783</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2861751</t>
+          <t>2859621</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2930246</t>
+          <t>2929945</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2952014</t>
+          <t>2949403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3023578</t>
+          <t>3023021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5833325</t>
+          <t>5833430</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5936848</t>
+          <t>5931113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>259211</t>
+          <t>256541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>320905</t>
+          <t>326232</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>251516</t>
+          <t>256036</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>320428</t>
+          <t>321217</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526663</t>
+          <t>533690</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>623516</t>
+          <t>626340</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75171</t>
+          <t>77251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>56876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>90920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107483</t>
+          <t>109209</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156963</t>
+          <t>154712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>665947</t>
+          <t>666079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>683734</t>
+          <t>684313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>648410</t>
+          <t>646657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>671199</t>
+          <t>670666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1321111</t>
+          <t>1322763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1350936</t>
+          <t>1351186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27753</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31628</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59660</t>
+          <t>58534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>891716</t>
+          <t>894693</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>934549</t>
+          <t>933989</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>906284</t>
+          <t>908322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>947672</t>
+          <t>947285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1816733</t>
+          <t>1817617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870262</t>
+          <t>1871405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52993</t>
+          <t>52534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89181</t>
+          <t>86906</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57277</t>
+          <t>57421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94572</t>
+          <t>90288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118844</t>
+          <t>118749</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>168293</t>
+          <t>166504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>40562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35158</t>
+          <t>34430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63969</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>670827</t>
+          <t>672560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>706598</t>
+          <t>705582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>698379</t>
+          <t>697855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>728680</t>
+          <t>727484</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1382057</t>
+          <t>1382257</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1426983</t>
+          <t>1427877</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>40455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69444</t>
+          <t>69503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38812</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>69755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87895</t>
+          <t>86067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129403</t>
+          <t>129860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>23066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>792283</t>
+          <t>796618</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>837666</t>
+          <t>838542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>893295</t>
+          <t>891097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>934070</t>
+          <t>933103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1702155</t>
+          <t>1701931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1761505</t>
+          <t>1759857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71716</t>
+          <t>72481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111123</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74487</t>
+          <t>74474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110714</t>
+          <t>111919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155185</t>
+          <t>154393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207201</t>
+          <t>207420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41603</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43952</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44854</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77573</t>
+          <t>76339</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3066346</t>
+          <t>3063336</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3135577</t>
+          <t>3131206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3185672</t>
+          <t>3184442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3254090</t>
+          <t>3254864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6271932</t>
+          <t>6271385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6368819</t>
+          <t>6367958</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199968</t>
+          <t>199682</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>260202</t>
+          <t>264374</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>211171</t>
+          <t>210645</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>274378</t>
+          <t>273717</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>428126</t>
+          <t>433378</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>517208</t>
+          <t>518549</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>55021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89074</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47863</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>79311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107265</t>
+          <t>109538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154609</t>
+          <t>156782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016 (tasa de respuesta: 99,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>620095</t>
+          <t>618500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>643247</t>
+          <t>642225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>627870</t>
+          <t>627906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>649155</t>
+          <t>649066</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1255128</t>
+          <t>1256236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1286326</t>
+          <t>1287613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43858</t>
+          <t>45659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42699</t>
+          <t>42029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71950</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>887780</t>
+          <t>884894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>926850</t>
+          <t>927533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>889278</t>
+          <t>888913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>933767</t>
+          <t>932607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1791887</t>
+          <t>1793313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1850203</t>
+          <t>1850955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88641</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62735</t>
+          <t>62381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99752</t>
+          <t>98372</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128485</t>
+          <t>125706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>177106</t>
+          <t>175470</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24642</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48629</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31330</t>
+          <t>33230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60407</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61878</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98366</t>
+          <t>98027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>582292</t>
+          <t>581450</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>627622</t>
+          <t>627023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>610478</t>
+          <t>608851</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>654040</t>
+          <t>653901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1207728</t>
+          <t>1206325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1273324</t>
+          <t>1269718</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79045</t>
+          <t>79555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116693</t>
+          <t>118674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76794</t>
+          <t>75898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113337</t>
+          <t>113411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166078</t>
+          <t>164957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218674</t>
+          <t>217188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>36916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66754</t>
+          <t>64853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37550</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66184</t>
+          <t>64945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80547</t>
+          <t>79356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120184</t>
+          <t>121195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>833389</t>
+          <t>833875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>869185</t>
+          <t>868283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>923857</t>
+          <t>925033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>959741</t>
+          <t>962184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1770955</t>
+          <t>1771126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1819842</t>
+          <t>1822274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56713</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90549</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>58757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124774</t>
+          <t>122224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170761</t>
+          <t>170719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>25558</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2960710</t>
+          <t>2960910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3031771</t>
+          <t>3034251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3091658</t>
+          <t>3090149</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3168734</t>
+          <t>3173315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6074932</t>
+          <t>6076321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6182812</t>
+          <t>6178332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239058</t>
+          <t>240730</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>303879</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>239618</t>
+          <t>238231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>306473</t>
+          <t>309171</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>502946</t>
+          <t>500042</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>593440</t>
+          <t>588658</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76785</t>
+          <t>78150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116673</t>
+          <t>117496</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88339</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131327</t>
+          <t>131241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174287</t>
+          <t>176594</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>233586</t>
+          <t>233361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>606103</t>
+          <t>604864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>622403</t>
+          <t>622234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>696941</t>
+          <t>696153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>712705</t>
+          <t>713426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1310505</t>
+          <t>1309063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1332911</t>
+          <t>1332820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>24070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>26094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18931</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>40102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1116318</t>
+          <t>1114716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1163946</t>
+          <t>1165147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>889093</t>
+          <t>891514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>917438</t>
+          <t>916662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2020714</t>
+          <t>2021297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2081856</t>
+          <t>2084634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43418</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48186</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39968</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79140</t>
+          <t>78014</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>39699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>26856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>57672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>647863</t>
+          <t>645845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>674974</t>
+          <t>676205</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>878037</t>
+          <t>878273</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>911536</t>
+          <t>910538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1535672</t>
+          <t>1535646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1583576</t>
+          <t>1582564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52981</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47302</t>
+          <t>46633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>44051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90660</t>
+          <t>90117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>851300</t>
+          <t>849779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>884464</t>
+          <t>884617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1013262</t>
+          <t>1012632</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1043551</t>
+          <t>1042783</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1875459</t>
+          <t>1873624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1921442</t>
+          <t>1919238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>27777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54120</t>
+          <t>55102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32093</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65194</t>
+          <t>67043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101535</t>
+          <t>103351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49817</t>
+          <t>52817</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3258294</t>
+          <t>3259777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3323429</t>
+          <t>3328401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3508070</t>
+          <t>3507655</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3564220</t>
+          <t>3565796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6777796</t>
+          <t>6780341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6873882</t>
+          <t>6875701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88013</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142201</t>
+          <t>142670</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99846</t>
+          <t>99628</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145798</t>
+          <t>148752</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>201309</t>
+          <t>202757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>278304</t>
+          <t>276070</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>64222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52958</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66776</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109239</t>
+          <t>109232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">

--- a/data/trans_orig/P05A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>609904</t>
+          <t>607881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>640434</t>
+          <t>638946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>606878</t>
+          <t>605983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>637109</t>
+          <t>635591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1227841</t>
+          <t>1224608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1270806</t>
+          <t>1268764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46842</t>
+          <t>47222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76484</t>
+          <t>76872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63350</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90491</t>
+          <t>91292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129306</t>
+          <t>134219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28607</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>838694</t>
+          <t>839822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>878075</t>
+          <t>877579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>839245</t>
+          <t>838136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>879859</t>
+          <t>878452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1692589</t>
+          <t>1690833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1748027</t>
+          <t>1746190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62206</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97171</t>
+          <t>95269</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>61105</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93710</t>
+          <t>96501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128263</t>
+          <t>130226</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>178820</t>
+          <t>180046</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>27974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18347</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32825</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61622</t>
+          <t>59901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>567184</t>
+          <t>567479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>603599</t>
+          <t>602590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>584907</t>
+          <t>584338</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>618664</t>
+          <t>617927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1165418</t>
+          <t>1162542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1211969</t>
+          <t>1213069</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61658</t>
+          <t>62837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96765</t>
+          <t>96515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50386</t>
+          <t>49820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81269</t>
+          <t>80897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120909</t>
+          <t>122896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165793</t>
+          <t>167087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>803087</t>
+          <t>802074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>839903</t>
+          <t>841008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>877890</t>
+          <t>877437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>919329</t>
+          <t>919577</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1693975</t>
+          <t>1694646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1749025</t>
+          <t>1749505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59112</t>
+          <t>58904</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90286</t>
+          <t>91130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79178</t>
+          <t>78872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115691</t>
+          <t>117539</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146674</t>
+          <t>148617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196333</t>
+          <t>198597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>36694</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29233</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>32929</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59783</t>
+          <t>58366</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2859621</t>
+          <t>2860945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2929945</t>
+          <t>2930565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2949403</t>
+          <t>2948078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3023021</t>
+          <t>3020706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5833430</t>
+          <t>5832637</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5931113</t>
+          <t>5933824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>256541</t>
+          <t>259641</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>326232</t>
+          <t>322953</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256036</t>
+          <t>255920</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>321217</t>
+          <t>321049</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>533690</t>
+          <t>529305</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>626340</t>
+          <t>622290</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>43623</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>73968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56876</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90920</t>
+          <t>93521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109209</t>
+          <t>108198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>154413</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>666079</t>
+          <t>665519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>684313</t>
+          <t>684399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>646657</t>
+          <t>647834</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>670666</t>
+          <t>671819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1322763</t>
+          <t>1321801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1351186</t>
+          <t>1351997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37726</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>894693</t>
+          <t>894087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>933989</t>
+          <t>933048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908322</t>
+          <t>909059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>947285</t>
+          <t>948963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1817617</t>
+          <t>1815770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1871405</t>
+          <t>1871569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52534</t>
+          <t>53857</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86906</t>
+          <t>89265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57421</t>
+          <t>56796</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90288</t>
+          <t>92039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118749</t>
+          <t>119465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>166504</t>
+          <t>166487</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31131</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61890</t>
+          <t>64170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>672560</t>
+          <t>673030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>705582</t>
+          <t>707284</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>697855</t>
+          <t>697976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>727484</t>
+          <t>728379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1382257</t>
+          <t>1385340</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1427877</t>
+          <t>1429804</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69503</t>
+          <t>69259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40802</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69755</t>
+          <t>68477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86067</t>
+          <t>86535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129860</t>
+          <t>126965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>796618</t>
+          <t>793444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>838542</t>
+          <t>835793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>891097</t>
+          <t>891598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>933103</t>
+          <t>934070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1701931</t>
+          <t>1699126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1759857</t>
+          <t>1758405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72481</t>
+          <t>73201</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>110270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74474</t>
+          <t>73725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111919</t>
+          <t>111424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154393</t>
+          <t>154169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207420</t>
+          <t>208174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>43953</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45136</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76339</t>
+          <t>77705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3063336</t>
+          <t>3064807</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3131206</t>
+          <t>3134388</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3184442</t>
+          <t>3186366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3254864</t>
+          <t>3256922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6271385</t>
+          <t>6271941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6367958</t>
+          <t>6366356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199682</t>
+          <t>200100</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>264374</t>
+          <t>259272</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>210645</t>
+          <t>213410</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>273717</t>
+          <t>273167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>433378</t>
+          <t>431257</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55021</t>
+          <t>53481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89029</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>45780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79311</t>
+          <t>78541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109538</t>
+          <t>108450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156782</t>
+          <t>158076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>618500</t>
+          <t>618982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>642225</t>
+          <t>642838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>627906</t>
+          <t>627955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>649066</t>
+          <t>650100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1256236</t>
+          <t>1255314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1287613</t>
+          <t>1286305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>44363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72174</t>
+          <t>71407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>884894</t>
+          <t>886080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>927533</t>
+          <t>927482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>888913</t>
+          <t>892783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>932607</t>
+          <t>934382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1793313</t>
+          <t>1790963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1850955</t>
+          <t>1850112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55679</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88562</t>
+          <t>89290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,82 +6341,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>78760</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>62417</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>97521</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>149441</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>127677</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>179341</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>8,74%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>78760</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>62381</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>98372</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>149441</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>125706</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>175470</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>49478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33230</t>
+          <t>32557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60012</t>
+          <t>59874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>62830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98027</t>
+          <t>99555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>581450</t>
+          <t>582106</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>627023</t>
+          <t>628938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>608851</t>
+          <t>610131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>653901</t>
+          <t>653937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1206325</t>
+          <t>1206886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1269718</t>
+          <t>1267289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79555</t>
+          <t>78831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118674</t>
+          <t>115786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75898</t>
+          <t>74623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113411</t>
+          <t>112868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164957</t>
+          <t>165863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217188</t>
+          <t>218799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36916</t>
+          <t>37741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64853</t>
+          <t>66676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36826</t>
+          <t>37029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>65028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79356</t>
+          <t>81007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121195</t>
+          <t>119724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>833875</t>
+          <t>834581</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>868283</t>
+          <t>868792</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>925033</t>
+          <t>923930</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>962184</t>
+          <t>960883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1771126</t>
+          <t>1771326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1822274</t>
+          <t>1820568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>55802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89230</t>
+          <t>88898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58757</t>
+          <t>59595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94239</t>
+          <t>95027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122224</t>
+          <t>125013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170719</t>
+          <t>172109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25558</t>
+          <t>25509</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2960910</t>
+          <t>2959044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3034251</t>
+          <t>3032837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3090149</t>
+          <t>3093712</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3173315</t>
+          <t>3169131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6076321</t>
+          <t>6076649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6178332</t>
+          <t>6180294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240730</t>
+          <t>240699</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>303745</t>
+          <t>308118</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>238231</t>
+          <t>239705</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>309171</t>
+          <t>303774</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500042</t>
+          <t>497706</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>588658</t>
+          <t>584045</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78150</t>
+          <t>76059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117496</t>
+          <t>114556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>88252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131241</t>
+          <t>129105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176594</t>
+          <t>174575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>233361</t>
+          <t>234176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>615185</t>
+          <t>669985</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>604864</t>
+          <t>659895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>622234</t>
+          <t>676519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>707126</t>
+          <t>714493</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>696153</t>
+          <t>703267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>713426</t>
+          <t>720878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,17 +8334,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1322311</t>
+          <t>1384477</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1309063</t>
+          <t>1371410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1332820</t>
+          <t>1394847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19303</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40102</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,22 +8525,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1359086</t>
+          <t>1423103</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359086</t>
+          <t>1423103</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1359086</t>
+          <t>1423103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1139059</t>
+          <t>985941</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1114716</t>
+          <t>966536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1165147</t>
+          <t>1000252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>905758</t>
+          <t>1013738</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>891514</t>
+          <t>996789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>916662</t>
+          <t>1026511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2044818</t>
+          <t>1999679</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2021297</t>
+          <t>1975692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2084634</t>
+          <t>2020394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43418</t>
+          <t>49593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24770</t>
+          <t>27048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47072</t>
+          <t>51769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61342</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36815</t>
+          <t>56067</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78014</t>
+          <t>89671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>41770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26856</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>46505</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57672</t>
+          <t>62839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1191438</t>
+          <t>1047530</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1191438</t>
+          <t>1047530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1191438</t>
+          <t>1047530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>957043</t>
+          <t>1069667</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957043</t>
+          <t>1069667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>957043</t>
+          <t>1069667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2148482</t>
+          <t>2117197</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2148482</t>
+          <t>2117197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2148482</t>
+          <t>2117197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>664265</t>
+          <t>755283</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645845</t>
+          <t>737821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>676205</t>
+          <t>769342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,34 +9211,34 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>893025</t>
+          <t>761785</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>878273</t>
+          <t>748818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>910538</t>
+          <t>772056</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>96,4%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1623</t>
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1557290</t>
+          <t>1517068</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1535646</t>
+          <t>1494885</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1582564</t>
+          <t>1533816</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -9289,17 +9289,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>42362</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56635</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>37632</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46633</t>
+          <t>50061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>69166</t>
+          <t>79994</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44051</t>
+          <t>63555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90117</t>
+          <t>99223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -9402,102 +9402,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4345</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1672</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>10426</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5461</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3395</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7856</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>703519</t>
+          <t>800908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>703519</t>
+          <t>800908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>703519</t>
+          <t>800908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>926332</t>
+          <t>800849</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>926332</t>
+          <t>800849</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>926332</t>
+          <t>800849</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1629851</t>
+          <t>1601756</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1629851</t>
+          <t>1601756</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1629851</t>
+          <t>1601756</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>870835</t>
+          <t>932096</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>849779</t>
+          <t>912118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>884617</t>
+          <t>945891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1028632</t>
+          <t>1047371</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1012632</t>
+          <t>1032550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1042783</t>
+          <t>1058946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1899468</t>
+          <t>1979467</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1873624</t>
+          <t>1956438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1919238</t>
+          <t>1999035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55102</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44243</t>
+          <t>48613</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32943</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57426</t>
+          <t>62666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,27 +9815,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>82390</t>
+          <t>88844</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67043</t>
+          <t>72778</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103351</t>
+          <t>107668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,17 +9893,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>32005</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52817</t>
+          <t>47351</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>924752</t>
+          <t>987049</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>924752</t>
+          <t>987049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>924752</t>
+          <t>987049</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1089719</t>
+          <t>1113268</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1089719</t>
+          <t>1113268</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1089719</t>
+          <t>1113268</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2014472</t>
+          <t>2100317</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2014472</t>
+          <t>2100317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2014472</t>
+          <t>2100317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3289346</t>
+          <t>3343306</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3259777</t>
+          <t>3314395</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3328401</t>
+          <t>3370911</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3534542</t>
+          <t>3537386</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3507655</t>
+          <t>3512316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3565796</t>
+          <t>3559969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6823887</t>
+          <t>6880691</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6780341</t>
+          <t>6839413</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6875701</t>
+          <t>6917096</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>117144</t>
+          <t>131360</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89749</t>
+          <t>108145</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142670</t>
+          <t>156622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>138125</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99628</t>
+          <t>117681</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148752</t>
+          <t>161519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>241383</t>
+          <t>269485</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>202757</t>
+          <t>237020</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>276070</t>
+          <t>302941</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64222</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>30891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52988</t>
+          <t>54542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>86620</t>
+          <t>92197</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65921</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109232</t>
+          <t>113622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3454132</t>
+          <t>3525111</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3454132</t>
+          <t>3525111</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3454132</t>
+          <t>3525111</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3697759</t>
+          <t>3717263</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3697759</t>
+          <t>3717263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3697759</t>
+          <t>3717263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7151890</t>
+          <t>7242373</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7151890</t>
+          <t>7242373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7151890</t>
+          <t>7242373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
